--- a/sap api.xlsx
+++ b/sap api.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\SAP\SAP_Monitoring_System\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7DF5791-05FF-43FF-AC46-D479C5E9982A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{956E345B-64E6-44D8-9520-77083F719ADD}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6810" xr2:uid="{6290779B-7ADC-4AF5-888D-C8DF0032F89E}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="47">
   <si>
     <t>Sr. No</t>
   </si>
@@ -142,6 +142,30 @@
   </si>
   <si>
     <t>Cancelled Jobs</t>
+  </si>
+  <si>
+    <t>http://mpcls4hdevapp.mpower.com.qa:8000/sap/bc/abap/z_strust_srv/strust?sap-client=150</t>
+  </si>
+  <si>
+    <t>STRUST certificates expired</t>
+  </si>
+  <si>
+    <t>http://mpclsapbip.mpower.com.qa:8080/BOE/CMC</t>
+  </si>
+  <si>
+    <t>https://mpclsapgws.mpower.com.qa:1443/sap/bc/ui2/flp?sap-system-login-oninputprocessing=onProceed&amp;sap-client=300&amp;sap-language=EN#Shell-home</t>
+  </si>
+  <si>
+    <t>https://mpclsapwdp.mpower.com.qa:8000/sap/wdisp/admin/public/default.html</t>
+  </si>
+  <si>
+    <t>BI PROD</t>
+  </si>
+  <si>
+    <t>FIORI URL</t>
+  </si>
+  <si>
+    <t>WEBDISPATCHER URL</t>
   </si>
 </sst>
 </file>
@@ -537,7 +561,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9FC83FB5-3B55-4A03-8A31-296AAB5E9A7A}">
-  <dimension ref="B2:D22"/>
+  <dimension ref="B2:D26"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="3" max="3" width="26.1796875" customWidth="1"/>
@@ -720,7 +744,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="18" spans="2:4" ht="58" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B18" s="2">
         <v>16</v>
       </c>
@@ -742,7 +766,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="20" spans="2:4" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B20" s="2">
         <v>18</v>
       </c>
@@ -773,6 +797,50 @@
       </c>
       <c r="D22" s="5" t="s">
         <v>37</v>
+      </c>
+    </row>
+    <row r="23" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B23" s="4">
+        <v>21</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="24" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B24" s="4">
+        <v>22</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="25" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B25" s="4">
+        <v>23</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="26" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B26" s="4">
+        <v>24</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -791,12 +859,16 @@
     <hyperlink ref="D14" r:id="rId12" xr:uid="{3DA67577-63E2-4E00-A043-F71EB80F9E51}"/>
     <hyperlink ref="D15" r:id="rId13" xr:uid="{DC37E5D7-1C82-4388-AF26-804DB5FEB4F5}"/>
     <hyperlink ref="D16" r:id="rId14" xr:uid="{F9442317-964F-480F-AF2B-42B5740FCAE0}"/>
-    <hyperlink ref="D17" r:id="rId15" tooltip="http://mpcls4hdevapp.mpower.com.qa:8000/sap/bc/abap/z_sm21_log_srv/sm21?sap-client=150" xr:uid="{5C1A7514-C9BA-48A1-8F6D-C38ED6C7178C}"/>
-    <hyperlink ref="D18" r:id="rId16" tooltip="http://mpcls4hdevapp.mpower.com.qa:8000/sap/bc/abap/z_sm58_trfc_srv/sm58?sap-client=150" xr:uid="{DC46EAC6-E5F5-4DAC-A721-AD35676EF7D3}"/>
+    <hyperlink ref="D17" r:id="rId15" xr:uid="{5C1A7514-C9BA-48A1-8F6D-C38ED6C7178C}"/>
+    <hyperlink ref="D18" r:id="rId16" xr:uid="{DC46EAC6-E5F5-4DAC-A721-AD35676EF7D3}"/>
     <hyperlink ref="D19" r:id="rId17" tooltip="http://mpcls4hdevapp.mpower.com.qa:8000/sap/bc/abap/z_st06_data_srv/st06?sap-client=150" xr:uid="{837656C6-575D-48EC-A9DD-CAE88EB71F3A}"/>
     <hyperlink ref="D20" r:id="rId18" tooltip="http://mpcls4hdevapp.mpower.com.qa:8000/sap/bc/abap/z_data_vol_srv/data_volume?sap-client=150" xr:uid="{1CA98820-0768-42D8-8682-E5A5DF75605C}"/>
     <hyperlink ref="D21" r:id="rId19" tooltip="http://mpcls4hdevapp.mpower.com.qa:8000/sap/bc/abap/z_data_vol_srv/data_volume?sap-client=150" display="http://mpcls4hdevapp.mpower.com.qa:8000/sap/bc/abap/z_data_vol_srv/data_volume?sap-client=150" xr:uid="{9494A5EA-26AE-48D1-9CC6-4ABC1D02FC73}"/>
     <hyperlink ref="D22" r:id="rId20" xr:uid="{6D2564C2-BC13-453F-9B0C-3DA3BB5FFEE6}"/>
+    <hyperlink ref="D23" r:id="rId21" xr:uid="{D7B17392-222A-45DF-BA8A-DBA8F1667821}"/>
+    <hyperlink ref="D24" r:id="rId22" xr:uid="{F3508B28-552E-4731-B2D4-4D6C03FEF13B}"/>
+    <hyperlink ref="D25" r:id="rId23" location="Shell-home" xr:uid="{FC419D54-450F-4183-AD25-53B307FF9969}"/>
+    <hyperlink ref="D26" r:id="rId24" xr:uid="{3F892F10-D955-4110-9906-A2D64B705959}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
